--- a/01_Raw_Data/One_Time_Efforts/2018_Sugarloaf_FireDistrict_PW.xlsx
+++ b/01_Raw_Data/One_Time_Efforts/2018_Sugarloaf_FireDistrict_PW.xlsx
@@ -1,16 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Shared drives\_CDPHE TEEO Data\_Enviro\PFAS\PFAS_Map_Series\PFAS_Map_Series_R\01_Raw_Data\One_Time_Efforts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11580"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="PrivateWell_Template_Format" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="SugarloafNoID_Jan2022" sheetId="2" r:id="rId5"/>
+    <sheet name="PrivateWell_Template_Format" sheetId="1" r:id="rId1"/>
+    <sheet name="Original" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">PrivateWell_Template_Format!$A$1:$X$1</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">SugarloafNoID_Jan2022!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Original!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PrivateWell_Template_Format!$A$1:$X$1</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="+NFg2AHohh6CcJhxOK14C1f6o/qWlttIQmmf/fs/Dbg="/>
@@ -20,14 +29,21 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="O20">
+    <comment ref="O20" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABM8NTZ3k
 Aki Suzuki - CDPHE    (2024-05-03 21:54:06)
 Can I assume with this dataset that "0" also means Non-detect? @kelsey.barton@state.co.us
@@ -35,11 +51,12 @@
 ID#AAABM8NTZ3o
 Aki Suzuki - CDPHE    (2024-05-03 21:57:25)
 Answer is yes</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgrTqltPqdqvqo5L7THGabrl2h8Jg=="/>
     </ext>
   </extLst>
@@ -47,14 +64,21 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="J20">
+    <comment ref="J20" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAABJqxvOOQ
 Aki Suzuki - CDPHE    (2024-05-03 21:54:06)
 Can I assume with this dataset that "0" also means Non-detect? @kelsey.barton@state.co.us
@@ -62,11 +86,12 @@
 ID#AAABJqxvOOU
 Aki Suzuki - CDPHE    (2024-05-03 21:57:25)
 Answer is yes</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhBr3JbboKdipHZDT5A2OGC0DL+qg=="/>
     </ext>
   </extLst>
@@ -265,31 +290,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000000000000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -299,54 +324,59 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -536,36 +566,36 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="13.43"/>
-    <col customWidth="1" min="2" max="2" width="12.0"/>
-    <col customWidth="1" min="3" max="3" width="16.86"/>
-    <col customWidth="1" min="4" max="4" width="17.86"/>
-    <col customWidth="1" min="5" max="5" width="8.71"/>
-    <col customWidth="1" min="6" max="6" width="12.29"/>
-    <col customWidth="1" min="7" max="7" width="19.0"/>
-    <col customWidth="1" min="8" max="8" width="26.57"/>
-    <col customWidth="1" min="9" max="16" width="12.43"/>
-    <col customWidth="1" min="17" max="17" width="8.71"/>
-    <col customWidth="1" min="18" max="19" width="12.29"/>
-    <col customWidth="1" min="20" max="20" width="13.57"/>
-    <col customWidth="1" min="21" max="21" width="14.14"/>
-    <col customWidth="1" min="22" max="22" width="19.0"/>
-    <col customWidth="1" min="23" max="23" width="14.86"/>
-    <col customWidth="1" min="24" max="24" width="16.29"/>
-    <col customWidth="1" min="25" max="26" width="8.71"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="26.5703125" customWidth="1"/>
+    <col min="9" max="16" width="12.42578125" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="12.28515625" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" customWidth="1"/>
+    <col min="22" max="22" width="19" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" customWidth="1"/>
+    <col min="24" max="24" width="16.28515625" customWidth="1"/>
+    <col min="25" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,9 +659,9 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>43230.0</v>
+        <v>43230</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>18</v>
@@ -640,7 +670,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="7">
-        <v>40.0167425</v>
+        <v>40.016742499999999</v>
       </c>
       <c r="F2" s="7">
         <v>-105.357846</v>
@@ -652,26 +682,26 @@
         <v>21</v>
       </c>
       <c r="I2" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="7">
-        <v>220.0</v>
+        <v>220</v>
       </c>
       <c r="K2" s="7">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L2" s="7">
-        <v>260.0</v>
+        <v>260</v>
       </c>
       <c r="M2" s="7">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="O2" s="7">
-        <f t="shared" ref="O2:O3" si="1">J2+K2</f>
+        <f t="shared" ref="O2:O3" si="0">J2+K2</f>
         <v>234</v>
       </c>
       <c r="P2" s="7">
-        <v>563.0</v>
+        <v>563</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>22</v>
@@ -680,9 +710,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>43230.0</v>
+        <v>43230</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>24</v>
@@ -691,7 +721,7 @@
         <v>19</v>
       </c>
       <c r="E3" s="7">
-        <v>40.0187042</v>
+        <v>40.018704200000002</v>
       </c>
       <c r="F3" s="7">
         <v>-105.4047364</v>
@@ -703,26 +733,26 @@
         <v>21</v>
       </c>
       <c r="I3" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="7">
-        <v>1200.0</v>
+        <v>1200</v>
       </c>
       <c r="K3" s="7">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="L3" s="7">
-        <v>540.0</v>
+        <v>540</v>
       </c>
       <c r="M3" s="7">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="O3" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1282</v>
       </c>
       <c r="P3" s="7">
-        <v>1880.0</v>
+        <v>1880</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>22</v>
@@ -731,9 +761,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>43252.0</v>
+        <v>43252</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>25</v>
@@ -742,7 +772,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="7">
-        <v>40.0248309</v>
+        <v>40.024830899999998</v>
       </c>
       <c r="F4" s="7">
         <v>-105.3874422</v>
@@ -754,7 +784,7 @@
         <v>21</v>
       </c>
       <c r="I4" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>26</v>
@@ -769,7 +799,7 @@
         <v>26</v>
       </c>
       <c r="O4" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P4" s="7" t="s">
         <v>26</v>
@@ -781,9 +811,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>27</v>
@@ -792,10 +822,10 @@
         <v>19</v>
       </c>
       <c r="E5" s="7">
-        <v>40.016913</v>
+        <v>40.016913000000002</v>
       </c>
       <c r="F5" s="7">
-        <v>-105.4030359</v>
+        <v>-105.40303590000001</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>20</v>
@@ -804,7 +834,7 @@
         <v>21</v>
       </c>
       <c r="I5" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="7">
         <v>4.7</v>
@@ -813,7 +843,7 @@
         <v>5.3</v>
       </c>
       <c r="L5" s="7">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="M5" s="7">
         <v>6.4</v>
@@ -832,9 +862,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>28</v>
@@ -843,7 +873,7 @@
         <v>19</v>
       </c>
       <c r="E6" s="7">
-        <v>40.0181948</v>
+        <v>40.018194800000003</v>
       </c>
       <c r="F6" s="7">
         <v>-105.4018289</v>
@@ -855,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="I6" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>26</v>
@@ -870,7 +900,7 @@
         <v>26</v>
       </c>
       <c r="O6" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>26</v>
@@ -882,9 +912,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>29</v>
@@ -905,26 +935,26 @@
         <v>21</v>
       </c>
       <c r="I7" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="7">
-        <v>210.0</v>
+        <v>210</v>
       </c>
       <c r="K7" s="7">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="L7" s="7">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="M7" s="7">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="O7" s="7">
         <f>J7+K7</f>
         <v>256</v>
       </c>
       <c r="P7" s="7">
-        <v>569.0</v>
+        <v>569</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>22</v>
@@ -933,9 +963,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>30</v>
@@ -944,10 +974,10 @@
         <v>19</v>
       </c>
       <c r="E8" s="7">
-        <v>40.022151</v>
+        <v>40.022151000000001</v>
       </c>
       <c r="F8" s="7">
-        <v>-105.4074723</v>
+        <v>-105.40747229999999</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>20</v>
@@ -956,7 +986,7 @@
         <v>21</v>
       </c>
       <c r="I8" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>26</v>
@@ -971,7 +1001,7 @@
         <v>26</v>
       </c>
       <c r="O8" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P8" s="7" t="s">
         <v>26</v>
@@ -983,9 +1013,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>31</v>
@@ -994,7 +1024,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="7">
-        <v>40.020783</v>
+        <v>40.020783000000002</v>
       </c>
       <c r="F9" s="7">
         <v>-105.4079121</v>
@@ -1006,7 +1036,7 @@
         <v>21</v>
       </c>
       <c r="I9" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>26</v>
@@ -1021,7 +1051,7 @@
         <v>26</v>
       </c>
       <c r="O9" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P9" s="7" t="s">
         <v>26</v>
@@ -1033,9 +1063,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>32</v>
@@ -1044,10 +1074,10 @@
         <v>19</v>
       </c>
       <c r="E10" s="7">
-        <v>40.0212759</v>
+        <v>40.021275899999999</v>
       </c>
       <c r="F10" s="7">
-        <v>-105.4037815</v>
+        <v>-105.40378149999999</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>20</v>
@@ -1056,7 +1086,7 @@
         <v>21</v>
       </c>
       <c r="I10" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>26</v>
@@ -1071,7 +1101,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P10" s="7" t="s">
         <v>26</v>
@@ -1083,9 +1113,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>33</v>
@@ -1094,7 +1124,7 @@
         <v>19</v>
       </c>
       <c r="E11" s="7">
-        <v>40.0198792</v>
+        <v>40.019879199999998</v>
       </c>
       <c r="F11" s="7">
         <v>-105.4034972</v>
@@ -1106,16 +1136,16 @@
         <v>21</v>
       </c>
       <c r="I11" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="7">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K11" s="7">
         <v>3.5</v>
       </c>
       <c r="L11" s="7">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="O11" s="7">
         <f>J11+K11</f>
@@ -1131,9 +1161,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>34</v>
@@ -1154,7 +1184,7 @@
         <v>21</v>
       </c>
       <c r="I12" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>26</v>
@@ -1169,7 +1199,7 @@
         <v>26</v>
       </c>
       <c r="O12" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>26</v>
@@ -1181,9 +1211,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>35</v>
@@ -1192,7 +1222,7 @@
         <v>19</v>
       </c>
       <c r="E13" s="7">
-        <v>40.0192588</v>
+        <v>40.019258800000003</v>
       </c>
       <c r="F13" s="7">
         <v>-105.4088134</v>
@@ -1204,13 +1234,13 @@
         <v>21</v>
       </c>
       <c r="I13" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>26</v>
       </c>
       <c r="K13" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1219,10 +1249,10 @@
         <v>26</v>
       </c>
       <c r="O13" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P13" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>22</v>
@@ -1231,9 +1261,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>36</v>
@@ -1242,7 +1272,7 @@
         <v>19</v>
       </c>
       <c r="E14" s="7">
-        <v>40.0169417</v>
+        <v>40.016941699999997</v>
       </c>
       <c r="F14" s="7">
         <v>-105.4085398</v>
@@ -1254,7 +1284,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>26</v>
@@ -1269,7 +1299,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P14" s="7" t="s">
         <v>26</v>
@@ -1281,9 +1311,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>43255.0</v>
+        <v>43255</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>37</v>
@@ -1292,7 +1322,7 @@
         <v>19</v>
       </c>
       <c r="E15" s="7">
-        <v>40.0166028</v>
+        <v>40.016602800000001</v>
       </c>
       <c r="F15" s="7">
         <v>-105.3564137</v>
@@ -1304,25 +1334,25 @@
         <v>21</v>
       </c>
       <c r="I15" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L15" s="7">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>26</v>
       </c>
       <c r="O15" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="P15" s="7">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>22</v>
@@ -1331,9 +1361,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>43255.0</v>
+        <v>43255</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>38</v>
@@ -1342,7 +1372,7 @@
         <v>19</v>
       </c>
       <c r="E16" s="7">
-        <v>40.0167384</v>
+        <v>40.016738400000001</v>
       </c>
       <c r="F16" s="7">
         <v>-105.354681</v>
@@ -1354,10 +1384,10 @@
         <v>21</v>
       </c>
       <c r="I16" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="7">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="K16" s="7">
         <v>6.4</v>
@@ -1382,9 +1412,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>43288.0</v>
+        <v>43288</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>39</v>
@@ -1393,10 +1423,10 @@
         <v>19</v>
       </c>
       <c r="E17" s="7">
-        <v>40.0239098</v>
+        <v>40.023909799999998</v>
       </c>
       <c r="F17" s="7">
-        <v>-105.3834551</v>
+        <v>-105.38345510000001</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>20</v>
@@ -1405,7 +1435,7 @@
         <v>21</v>
       </c>
       <c r="I17" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>26</v>
@@ -1420,7 +1450,7 @@
         <v>26</v>
       </c>
       <c r="O17" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P17" s="7" t="s">
         <v>26</v>
@@ -1432,9 +1462,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>43295.0</v>
+        <v>43295</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>40</v>
@@ -1443,7 +1473,7 @@
         <v>19</v>
       </c>
       <c r="E18" s="7">
-        <v>40.0256553</v>
+        <v>40.025655299999997</v>
       </c>
       <c r="F18" s="7">
         <v>-105.388566</v>
@@ -1455,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I18" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>26</v>
@@ -1470,7 +1500,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P18" s="7" t="s">
         <v>26</v>
@@ -1482,9 +1512,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>43312.0</v>
+        <v>43312</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>41</v>
@@ -1493,7 +1523,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="7">
-        <v>40.0214822</v>
+        <v>40.021482200000001</v>
       </c>
       <c r="F19" s="7">
         <v>-105.3802852</v>
@@ -1505,7 +1535,7 @@
         <v>21</v>
       </c>
       <c r="I19" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>26</v>
@@ -1520,7 +1550,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P19" s="7" t="s">
         <v>26</v>
@@ -1532,9 +1562,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>42</v>
@@ -1543,7 +1573,7 @@
         <v>19</v>
       </c>
       <c r="E20" s="7">
-        <v>40.0152604</v>
+        <v>40.015260400000003</v>
       </c>
       <c r="F20" s="7">
         <v>-105.3543104</v>
@@ -1555,7 +1585,7 @@
         <v>21</v>
       </c>
       <c r="I20" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>26</v>
@@ -1570,10 +1600,10 @@
         <v>26</v>
       </c>
       <c r="O20" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P20" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="7" t="s">
         <v>22</v>
@@ -1582,9 +1612,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>43</v>
@@ -1605,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="I21" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>26</v>
@@ -1623,7 +1653,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P21" s="7" t="s">
         <v>26</v>
@@ -1635,9 +1665,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>44</v>
@@ -1646,7 +1676,7 @@
         <v>19</v>
       </c>
       <c r="E22" s="7">
-        <v>40.0167937</v>
+        <v>40.016793700000001</v>
       </c>
       <c r="F22" s="7">
         <v>-105.3531777</v>
@@ -1658,16 +1688,16 @@
         <v>21</v>
       </c>
       <c r="I22" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>26</v>
       </c>
       <c r="K22" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="7">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>26</v>
@@ -1676,10 +1706,10 @@
         <v>26</v>
       </c>
       <c r="O22" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P22" s="7">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>22</v>
@@ -1688,9 +1718,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>45</v>
@@ -1699,7 +1729,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="7">
-        <v>40.0136972</v>
+        <v>40.013697200000003</v>
       </c>
       <c r="F23" s="7">
         <v>-105.352542</v>
@@ -1711,7 +1741,7 @@
         <v>21</v>
       </c>
       <c r="I23" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>26</v>
@@ -1726,7 +1756,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P23" s="7" t="s">
         <v>26</v>
@@ -1738,9 +1768,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>46</v>
@@ -1749,7 +1779,7 @@
         <v>19</v>
       </c>
       <c r="E24" s="7">
-        <v>40.0233557</v>
+        <v>40.023355700000003</v>
       </c>
       <c r="F24" s="7">
         <v>-105.4058193</v>
@@ -1761,7 +1791,7 @@
         <v>21</v>
       </c>
       <c r="I24" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>26</v>
@@ -1779,7 +1809,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P24" s="7" t="s">
         <v>26</v>
@@ -1791,9 +1821,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>47</v>
@@ -1805,7 +1835,7 @@
         <v>40.0162707</v>
       </c>
       <c r="F25" s="7">
-        <v>-105.3553923</v>
+        <v>-105.35539230000001</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>20</v>
@@ -1814,22 +1844,22 @@
         <v>21</v>
       </c>
       <c r="I25" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="7">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="K25" s="7">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="L25" s="7">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="M25" s="7">
         <v>7.5</v>
       </c>
       <c r="N25" s="7">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="O25" s="7">
         <f>J25+K25</f>
@@ -1845,9 +1875,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>48</v>
@@ -1856,10 +1886,10 @@
         <v>19</v>
       </c>
       <c r="E26" s="7">
-        <v>40.0141788</v>
+        <v>40.014178800000003</v>
       </c>
       <c r="F26" s="7">
-        <v>-105.4035261</v>
+        <v>-105.40352609999999</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>20</v>
@@ -1868,7 +1898,7 @@
         <v>21</v>
       </c>
       <c r="I26" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>26</v>
@@ -1886,7 +1916,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P26" s="7" t="s">
         <v>26</v>
@@ -1898,9 +1928,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>49</v>
@@ -1909,7 +1939,7 @@
         <v>19</v>
       </c>
       <c r="E27" s="7">
-        <v>40.0178478</v>
+        <v>40.017847799999998</v>
       </c>
       <c r="F27" s="7">
         <v>-105.3567925</v>
@@ -1921,7 +1951,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>26</v>
@@ -1939,7 +1969,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P27" s="7" t="s">
         <v>26</v>
@@ -1951,9 +1981,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>50</v>
@@ -1962,10 +1992,10 @@
         <v>19</v>
       </c>
       <c r="E28" s="7">
-        <v>40.0162244</v>
+        <v>40.016224399999999</v>
       </c>
       <c r="F28" s="7">
-        <v>-105.4006185</v>
+        <v>-105.40061849999999</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>20</v>
@@ -1974,16 +2004,16 @@
         <v>21</v>
       </c>
       <c r="I28" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K28" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="M28" s="7" t="s">
         <v>26</v>
@@ -1992,11 +2022,11 @@
         <v>26</v>
       </c>
       <c r="O28" s="7">
-        <f t="shared" ref="O28:O29" si="2">J28+K28</f>
+        <f t="shared" ref="O28:O29" si="1">J28+K28</f>
         <v>9</v>
       </c>
       <c r="P28" s="7">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="Q28" s="7" t="s">
         <v>22</v>
@@ -2005,9 +2035,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>51</v>
@@ -2016,7 +2046,7 @@
         <v>19</v>
       </c>
       <c r="E29" s="7">
-        <v>40.0181806</v>
+        <v>40.018180600000001</v>
       </c>
       <c r="F29" s="7">
         <v>-105.4037338</v>
@@ -2028,29 +2058,29 @@
         <v>21</v>
       </c>
       <c r="I29" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="7">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="K29" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="L29" s="7">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>26</v>
       </c>
       <c r="N29" s="7">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="O29" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="P29" s="7">
-        <v>155.0</v>
+        <v>155</v>
       </c>
       <c r="Q29" s="7" t="s">
         <v>22</v>
@@ -2059,9 +2089,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>52</v>
@@ -2070,10 +2100,10 @@
         <v>19</v>
       </c>
       <c r="E30" s="7">
-        <v>40.0149189</v>
+        <v>40.014918899999998</v>
       </c>
       <c r="F30" s="7">
-        <v>-105.405859</v>
+        <v>-105.40585900000001</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>20</v>
@@ -2082,7 +2112,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>26</v>
@@ -2100,7 +2130,7 @@
         <v>26</v>
       </c>
       <c r="O30" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P30" s="7" t="s">
         <v>26</v>
@@ -2112,9 +2142,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>53</v>
@@ -2123,7 +2153,7 @@
         <v>19</v>
       </c>
       <c r="E31" s="7">
-        <v>40.0140848</v>
+        <v>40.014084799999999</v>
       </c>
       <c r="F31" s="7">
         <v>-105.3584098</v>
@@ -2135,7 +2165,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>26</v>
@@ -2153,7 +2183,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P31" s="7" t="s">
         <v>26</v>
@@ -2165,9 +2195,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>54</v>
@@ -2176,7 +2206,7 @@
         <v>19</v>
       </c>
       <c r="E32" s="7">
-        <v>40.0190106</v>
+        <v>40.019010600000001</v>
       </c>
       <c r="F32" s="7">
         <v>-105.3980536</v>
@@ -2188,7 +2218,7 @@
         <v>21</v>
       </c>
       <c r="I32" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>26</v>
@@ -2206,7 +2236,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P32" s="7" t="s">
         <v>26</v>
@@ -2218,9 +2248,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>55</v>
@@ -2229,7 +2259,7 @@
         <v>19</v>
       </c>
       <c r="E33" s="7">
-        <v>40.0226152</v>
+        <v>40.022615199999997</v>
       </c>
       <c r="F33" s="7">
         <v>-105.4025831</v>
@@ -2241,16 +2271,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L33" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>26</v>
@@ -2259,10 +2289,10 @@
         <v>26</v>
       </c>
       <c r="O33" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P33" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="Q33" s="7" t="s">
         <v>22</v>
@@ -2271,9 +2301,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>56</v>
@@ -2282,7 +2312,7 @@
         <v>19</v>
       </c>
       <c r="E34" s="7">
-        <v>40.0113931</v>
+        <v>40.011393099999999</v>
       </c>
       <c r="F34" s="7">
         <v>-105.3537632</v>
@@ -2294,7 +2324,7 @@
         <v>21</v>
       </c>
       <c r="I34" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>26</v>
@@ -2309,7 +2339,7 @@
         <v>26</v>
       </c>
       <c r="O34" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P34" s="7" t="s">
         <v>26</v>
@@ -2321,9 +2351,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>57</v>
@@ -2332,7 +2362,7 @@
         <v>19</v>
       </c>
       <c r="E35" s="7">
-        <v>40.0174771</v>
+        <v>40.017477100000001</v>
       </c>
       <c r="F35" s="7">
         <v>-105.3549852</v>
@@ -2344,7 +2374,7 @@
         <v>21</v>
       </c>
       <c r="I35" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>26</v>
@@ -2362,7 +2392,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P35" s="7" t="s">
         <v>26</v>
@@ -2374,9 +2404,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>58</v>
@@ -2388,7 +2418,7 @@
         <v>40.0135924</v>
       </c>
       <c r="F36" s="7">
-        <v>-105.3508914</v>
+        <v>-105.35089139999999</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>20</v>
@@ -2397,16 +2427,16 @@
         <v>21</v>
       </c>
       <c r="I36" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L36" s="7">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M36" s="7" t="s">
         <v>26</v>
@@ -2415,10 +2445,10 @@
         <v>26</v>
       </c>
       <c r="O36" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="P36" s="7">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="Q36" s="7" t="s">
         <v>22</v>
@@ -2427,1004 +2457,1000 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
-    <row r="65" ht="14.25" customHeight="1"/>
-    <row r="66" ht="14.25" customHeight="1"/>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1"/>
-    <row r="82" ht="14.25" customHeight="1"/>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
-    <row r="147" ht="14.25" customHeight="1"/>
-    <row r="148" ht="14.25" customHeight="1"/>
-    <row r="149" ht="14.25" customHeight="1"/>
-    <row r="150" ht="14.25" customHeight="1"/>
-    <row r="151" ht="14.25" customHeight="1"/>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="37" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="$A$1:$X$1">
-    <sortState ref="A1:X1">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="A1:X1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.71"/>
-    <col customWidth="1" min="2" max="3" width="9.57"/>
-    <col customWidth="1" min="4" max="4" width="18.86"/>
-    <col customWidth="1" min="5" max="5" width="8.71"/>
-    <col customWidth="1" min="6" max="6" width="11.57"/>
-    <col customWidth="1" min="7" max="9" width="8.71"/>
-    <col customWidth="1" min="10" max="10" width="16.0"/>
-    <col customWidth="1" min="11" max="13" width="8.71"/>
-    <col customWidth="1" min="14" max="14" width="13.0"/>
-    <col customWidth="1" min="15" max="26" width="8.71"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="3" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>59</v>
       </c>
@@ -3468,40 +3494,40 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="6">
-        <v>43230.0</v>
+        <v>43230</v>
       </c>
       <c r="C2" s="6">
-        <v>43230.0</v>
+        <v>43230</v>
       </c>
       <c r="D2" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7">
-        <v>220.0</v>
+        <v>220</v>
       </c>
       <c r="F2" s="7">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G2" s="7">
-        <v>260.0</v>
+        <v>260</v>
       </c>
       <c r="H2" s="7">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="J2" s="7">
-        <f t="shared" ref="J2:J3" si="1">E2+F2</f>
+        <f t="shared" ref="J2:J3" si="0">E2+F2</f>
         <v>234</v>
       </c>
       <c r="K2" s="7">
-        <v>563.0</v>
+        <v>563</v>
       </c>
       <c r="L2" s="7">
-        <v>40.0167425</v>
+        <v>40.016742499999999</v>
       </c>
       <c r="M2" s="7">
         <v>-105.357846</v>
@@ -3510,40 +3536,40 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="6">
-        <v>43191.0</v>
+        <v>43191</v>
       </c>
       <c r="C3" s="6">
-        <v>43230.0</v>
+        <v>43230</v>
       </c>
       <c r="D3" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="7">
-        <v>1200.0</v>
+        <v>1200</v>
       </c>
       <c r="F3" s="7">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="G3" s="7">
-        <v>540.0</v>
+        <v>540</v>
       </c>
       <c r="H3" s="7">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="J3" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1282</v>
       </c>
       <c r="K3" s="7">
-        <v>1880.0</v>
+        <v>1880</v>
       </c>
       <c r="L3" s="7">
-        <v>40.0187042</v>
+        <v>40.018704200000002</v>
       </c>
       <c r="M3" s="7">
         <v>-105.4047364</v>
@@ -3552,18 +3578,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="6">
-        <v>43252.0</v>
+        <v>43252</v>
       </c>
       <c r="C4" s="6">
-        <v>43252.0</v>
+        <v>43252</v>
       </c>
       <c r="D4" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>26</v>
@@ -3578,13 +3604,13 @@
         <v>26</v>
       </c>
       <c r="J4" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="7">
-        <v>40.0248309</v>
+        <v>40.024830899999998</v>
       </c>
       <c r="M4" s="7">
         <v>-105.3874422</v>
@@ -3593,18 +3619,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C5" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D5" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7">
         <v>4.7</v>
@@ -3613,7 +3639,7 @@
         <v>5.3</v>
       </c>
       <c r="G5" s="7">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="H5" s="7">
         <v>6.4</v>
@@ -3626,27 +3652,27 @@
         <v>34.4</v>
       </c>
       <c r="L5" s="7">
-        <v>40.016913</v>
+        <v>40.016913000000002</v>
       </c>
       <c r="M5" s="7">
-        <v>-105.4030359</v>
+        <v>-105.40303590000001</v>
       </c>
       <c r="N5" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B6" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C6" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D6" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>26</v>
@@ -3661,13 +3687,13 @@
         <v>26</v>
       </c>
       <c r="J6" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L6" s="7">
-        <v>40.0181948</v>
+        <v>40.018194800000003</v>
       </c>
       <c r="M6" s="7">
         <v>-105.4018289</v>
@@ -3676,37 +3702,37 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C7" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D7" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7">
-        <v>210.0</v>
+        <v>210</v>
       </c>
       <c r="F7" s="7">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="G7" s="7">
-        <v>290.0</v>
+        <v>290</v>
       </c>
       <c r="H7" s="7">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7">
         <f>E7+F7</f>
         <v>256</v>
       </c>
       <c r="K7" s="7">
-        <v>569.0</v>
+        <v>569</v>
       </c>
       <c r="L7" s="7">
         <v>40.0195176</v>
@@ -3718,18 +3744,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C8" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D8" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>26</v>
@@ -3744,33 +3770,33 @@
         <v>26</v>
       </c>
       <c r="J8" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="7">
-        <v>40.022151</v>
+        <v>40.022151000000001</v>
       </c>
       <c r="M8" s="7">
-        <v>-105.4074723</v>
+        <v>-105.40747229999999</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B9" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C9" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D9" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>26</v>
@@ -3785,13 +3811,13 @@
         <v>26</v>
       </c>
       <c r="J9" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="7">
-        <v>40.020783</v>
+        <v>40.020783000000002</v>
       </c>
       <c r="M9" s="7">
         <v>-105.4079121</v>
@@ -3800,18 +3826,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C10" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D10" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>26</v>
@@ -3826,42 +3852,42 @@
         <v>26</v>
       </c>
       <c r="J10" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L10" s="7">
-        <v>40.0212759</v>
+        <v>40.021275899999999</v>
       </c>
       <c r="M10" s="7">
-        <v>-105.4037815</v>
+        <v>-105.40378149999999</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C11" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D11" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="F11" s="7">
         <v>3.5</v>
       </c>
       <c r="G11" s="7">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="J11" s="7">
         <f>E11+F11</f>
@@ -3871,7 +3897,7 @@
         <v>54.5</v>
       </c>
       <c r="L11" s="7">
-        <v>40.0198792</v>
+        <v>40.019879199999998</v>
       </c>
       <c r="M11" s="7">
         <v>-105.4034972</v>
@@ -3880,18 +3906,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C12" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D12" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>26</v>
@@ -3906,7 +3932,7 @@
         <v>26</v>
       </c>
       <c r="J12" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>26</v>
@@ -3921,24 +3947,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C13" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D13" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>26</v>
@@ -3947,13 +3973,13 @@
         <v>26</v>
       </c>
       <c r="J13" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K13" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="7">
-        <v>40.0192588</v>
+        <v>40.019258800000003</v>
       </c>
       <c r="M13" s="7">
         <v>-105.4088134</v>
@@ -3962,18 +3988,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B14" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="C14" s="6">
-        <v>43254.0</v>
+        <v>43254</v>
       </c>
       <c r="D14" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>26</v>
@@ -3988,13 +4014,13 @@
         <v>26</v>
       </c>
       <c r="J14" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="7">
-        <v>40.0169417</v>
+        <v>40.016941699999997</v>
       </c>
       <c r="M14" s="7">
         <v>-105.4085398</v>
@@ -4003,39 +4029,39 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="6">
-        <v>43255.0</v>
+        <v>43255</v>
       </c>
       <c r="C15" s="6">
-        <v>43255.0</v>
+        <v>43255</v>
       </c>
       <c r="D15" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="7">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K15" s="7">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="L15" s="7">
-        <v>40.0166028</v>
+        <v>40.016602800000001</v>
       </c>
       <c r="M15" s="7">
         <v>-105.3564137</v>
@@ -4044,21 +4070,21 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B16" s="6">
-        <v>43255.0</v>
+        <v>43255</v>
       </c>
       <c r="C16" s="6">
-        <v>43255.0</v>
+        <v>43255</v>
       </c>
       <c r="D16" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F16" s="7">
         <v>6.4</v>
@@ -4077,7 +4103,7 @@
         <v>14.6</v>
       </c>
       <c r="L16" s="7">
-        <v>40.0167384</v>
+        <v>40.016738400000001</v>
       </c>
       <c r="M16" s="7">
         <v>-105.354681</v>
@@ -4086,18 +4112,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B17" s="6">
-        <v>43288.0</v>
+        <v>43288</v>
       </c>
       <c r="C17" s="6">
-        <v>43288.0</v>
+        <v>43288</v>
       </c>
       <c r="D17" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>26</v>
@@ -4112,33 +4138,33 @@
         <v>26</v>
       </c>
       <c r="J17" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L17" s="7">
-        <v>40.0239098</v>
+        <v>40.023909799999998</v>
       </c>
       <c r="M17" s="7">
-        <v>-105.3834551</v>
+        <v>-105.38345510000001</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="6">
-        <v>43295.0</v>
+        <v>43295</v>
       </c>
       <c r="C18" s="6">
-        <v>43295.0</v>
+        <v>43295</v>
       </c>
       <c r="D18" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>26</v>
@@ -4153,13 +4179,13 @@
         <v>26</v>
       </c>
       <c r="J18" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="7">
-        <v>40.0256553</v>
+        <v>40.025655299999997</v>
       </c>
       <c r="M18" s="7">
         <v>-105.388566</v>
@@ -4168,18 +4194,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="6">
-        <v>43312.0</v>
+        <v>43312</v>
       </c>
       <c r="C19" s="6">
-        <v>43312.0</v>
+        <v>43312</v>
       </c>
       <c r="D19" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>26</v>
@@ -4194,13 +4220,13 @@
         <v>26</v>
       </c>
       <c r="J19" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="7">
-        <v>40.0214822</v>
+        <v>40.021482200000001</v>
       </c>
       <c r="M19" s="7">
         <v>-105.3802852</v>
@@ -4209,18 +4235,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C20" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D20" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>26</v>
@@ -4235,13 +4261,13 @@
         <v>26</v>
       </c>
       <c r="J20" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L20" s="7">
-        <v>40.0152604</v>
+        <v>40.015260400000003</v>
       </c>
       <c r="M20" s="7">
         <v>-105.3543104</v>
@@ -4250,18 +4276,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>43</v>
       </c>
       <c r="B21" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C21" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D21" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>26</v>
@@ -4279,7 +4305,7 @@
         <v>26</v>
       </c>
       <c r="J21" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>26</v>
@@ -4294,27 +4320,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B22" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C22" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D22" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G22" s="7">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>26</v>
@@ -4323,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="J22" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K22" s="7">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="L22" s="7">
-        <v>40.0167937</v>
+        <v>40.016793700000001</v>
       </c>
       <c r="M22" s="7">
         <v>-105.3531777</v>
@@ -4338,18 +4364,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B23" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C23" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D23" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>26</v>
@@ -4364,13 +4390,13 @@
         <v>26</v>
       </c>
       <c r="J23" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L23" s="7">
-        <v>40.0136972</v>
+        <v>40.013697200000003</v>
       </c>
       <c r="M23" s="7">
         <v>-105.352542</v>
@@ -4379,18 +4405,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B24" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C24" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D24" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>26</v>
@@ -4408,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="J24" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="7">
-        <v>40.0233557</v>
+        <v>40.023355700000003</v>
       </c>
       <c r="M24" s="7">
         <v>-105.4058193</v>
@@ -4423,33 +4449,33 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B25" s="6">
-        <v>43277.0</v>
+        <v>43277</v>
       </c>
       <c r="C25" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D25" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E25" s="7">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="F25" s="7">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="G25" s="7">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="H25" s="7">
         <v>7.5</v>
       </c>
       <c r="I25" s="7">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="J25" s="7">
         <f>E25+F25</f>
@@ -4462,24 +4488,24 @@
         <v>40.0162707</v>
       </c>
       <c r="M25" s="7">
-        <v>-105.3553923</v>
+        <v>-105.35539230000001</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>48</v>
       </c>
       <c r="B26" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C26" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D26" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>26</v>
@@ -4497,33 +4523,33 @@
         <v>26</v>
       </c>
       <c r="J26" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L26" s="7">
-        <v>40.0141788</v>
+        <v>40.014178800000003</v>
       </c>
       <c r="M26" s="7">
-        <v>-105.4035261</v>
+        <v>-105.40352609999999</v>
       </c>
       <c r="N26" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B27" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C27" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D27" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>26</v>
@@ -4541,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="J27" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L27" s="7">
-        <v>40.0178478</v>
+        <v>40.017847799999998</v>
       </c>
       <c r="M27" s="7">
         <v>-105.3567925</v>
@@ -4556,27 +4582,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B28" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C28" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D28" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F28" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G28" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>26</v>
@@ -4585,59 +4611,59 @@
         <v>26</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" ref="J28:J29" si="2">E28+F28</f>
+        <f t="shared" ref="J28:J29" si="1">E28+F28</f>
         <v>9</v>
       </c>
       <c r="K28" s="7">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="L28" s="7">
-        <v>40.0162244</v>
+        <v>40.016224399999999</v>
       </c>
       <c r="M28" s="7">
-        <v>-105.4006185</v>
+        <v>-105.40061849999999</v>
       </c>
       <c r="N28" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B29" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C29" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D29" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="F29" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G29" s="7">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>26</v>
       </c>
       <c r="I29" s="7">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="J29" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="K29" s="7">
-        <v>155.0</v>
+        <v>155</v>
       </c>
       <c r="L29" s="7">
-        <v>40.0181806</v>
+        <v>40.018180600000001</v>
       </c>
       <c r="M29" s="7">
         <v>-105.4037338</v>
@@ -4646,18 +4672,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B30" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C30" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D30" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>26</v>
@@ -4675,33 +4701,33 @@
         <v>26</v>
       </c>
       <c r="J30" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L30" s="7">
-        <v>40.0149189</v>
+        <v>40.014918899999998</v>
       </c>
       <c r="M30" s="7">
-        <v>-105.405859</v>
+        <v>-105.40585900000001</v>
       </c>
       <c r="N30" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>53</v>
       </c>
       <c r="B31" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C31" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D31" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>26</v>
@@ -4719,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="J31" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L31" s="7">
-        <v>40.0140848</v>
+        <v>40.014084799999999</v>
       </c>
       <c r="M31" s="7">
         <v>-105.3584098</v>
@@ -4734,18 +4760,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B32" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C32" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D32" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>26</v>
@@ -4763,13 +4789,13 @@
         <v>26</v>
       </c>
       <c r="J32" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L32" s="7">
-        <v>40.0190106</v>
+        <v>40.019010600000001</v>
       </c>
       <c r="M32" s="7">
         <v>-105.3980536</v>
@@ -4778,27 +4804,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>55</v>
       </c>
       <c r="B33" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C33" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D33" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>26</v>
@@ -4807,13 +4833,13 @@
         <v>26</v>
       </c>
       <c r="J33" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K33" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="L33" s="7">
-        <v>40.0226152</v>
+        <v>40.022615199999997</v>
       </c>
       <c r="M33" s="7">
         <v>-105.4025831</v>
@@ -4822,18 +4848,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>56</v>
       </c>
       <c r="B34" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C34" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D34" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>26</v>
@@ -4848,13 +4874,13 @@
         <v>26</v>
       </c>
       <c r="J34" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="7">
-        <v>40.0113931</v>
+        <v>40.011393099999999</v>
       </c>
       <c r="M34" s="7">
         <v>-105.3537632</v>
@@ -4863,18 +4889,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>57</v>
       </c>
       <c r="B35" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C35" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D35" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>26</v>
@@ -4892,13 +4918,13 @@
         <v>26</v>
       </c>
       <c r="J35" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>26</v>
       </c>
       <c r="L35" s="7">
-        <v>40.0174771</v>
+        <v>40.017477100000001</v>
       </c>
       <c r="M35" s="7">
         <v>-105.3549852</v>
@@ -4907,27 +4933,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B36" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="C36" s="6">
-        <v>43331.0</v>
+        <v>43331</v>
       </c>
       <c r="D36" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="7">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>26</v>
@@ -4936,995 +4962,989 @@
         <v>26</v>
       </c>
       <c r="J36" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K36" s="7">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="L36" s="7">
         <v>40.0135924</v>
       </c>
       <c r="M36" s="7">
-        <v>-105.3508914</v>
+        <v>-105.35089139999999</v>
       </c>
       <c r="N36" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
-    <row r="65" ht="14.25" customHeight="1"/>
-    <row r="66" ht="14.25" customHeight="1"/>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1"/>
-    <row r="82" ht="14.25" customHeight="1"/>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
-    <row r="147" ht="14.25" customHeight="1"/>
-    <row r="148" ht="14.25" customHeight="1"/>
-    <row r="149" ht="14.25" customHeight="1"/>
-    <row r="150" ht="14.25" customHeight="1"/>
-    <row r="151" ht="14.25" customHeight="1"/>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="37" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="$A$1:$N$1">
-    <sortState ref="A1:N1">
-      <sortCondition ref="C1"/>
-    </sortState>
-  </autoFilter>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="A1:N1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>